--- a/data/trans_dic/P45C_R1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,48</t>
+          <t>1,5; 5,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,28</t>
+          <t>1,57; 6,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,19</t>
+          <t>0,35; 3,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,02</t>
+          <t>1,14; 5,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,86</t>
+          <t>1,17; 3,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,72</t>
+          <t>1,76; 4,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,06</t>
+          <t>1,8; 5,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,41</t>
+          <t>0,4; 2,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,57</t>
+          <t>0,17; 1,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,82</t>
+          <t>2,25; 6,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,62</t>
+          <t>1,6; 4,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,3</t>
+          <t>0,39; 2,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,84</t>
+          <t>3,45; 6,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,07</t>
+          <t>1,95; 4,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,28</t>
+          <t>0,28; 1,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,56</t>
+          <t>0,39; 1,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,21</t>
+          <t>3,37; 6,3</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,35</t>
+          <t>1,51; 5,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,64</t>
+          <t>0,05; 1,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,11</t>
+          <t>0,93; 3,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,88</t>
+          <t>0,02; 0,93</t>
         </is>
       </c>
     </row>
@@ -1137,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,22</t>
+          <t>1,51; 5,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,76</t>
+          <t>2,4; 7,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,62</t>
+          <t>0,26; 2,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,96</t>
+          <t>0,4; 2,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,48</t>
+          <t>2,41; 6,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,2</t>
+          <t>1,3; 4,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,88</t>
+          <t>0,86; 2,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,8</t>
+          <t>2,91; 6,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,12</t>
+          <t>1,09; 3,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,37</t>
+          <t>0,24; 1,41</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,57</t>
+          <t>0,36; 3,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,38</t>
+          <t>1,05; 4,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,38</t>
+          <t>0,37; 4,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,07</t>
+          <t>0,72; 4,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,91</t>
+          <t>1,31; 4,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,74</t>
+          <t>0,19; 1,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,97</t>
+          <t>0,71; 3,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,6</t>
+          <t>0,57; 2,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,97</t>
+          <t>1,48; 3,89</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,24</t>
+          <t>1,28; 4,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,89</t>
+          <t>0,34; 1,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,57</t>
+          <t>0,45; 2,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,33</t>
+          <t>1,14; 4,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,47</t>
+          <t>1,64; 4,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,87</t>
+          <t>0,9; 2,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,94</t>
+          <t>0,17; 1,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,82</t>
+          <t>0,53; 2,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,63</t>
+          <t>1,84; 3,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,96</t>
+          <t>0,81; 2,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,74</t>
+          <t>0,47; 1,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,89</t>
+          <t>0,96; 2,94</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,98</t>
+          <t>0,89; 2,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,28</t>
+          <t>0,15; 1,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,06</t>
+          <t>0,38; 2,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,69</t>
+          <t>1,51; 3,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,64</t>
+          <t>0,26; 1,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,59</t>
+          <t>0,26; 1,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,22 +1737,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,99</t>
+          <t>1,47; 2,99</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,94</t>
+          <t>0,26; 1,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,18</t>
+          <t>0,31; 1,15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,5</t>
+          <t>0,42; 1,4</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,19</t>
+          <t>1,28; 2,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,75</t>
+          <t>0,95; 1,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,32</t>
+          <t>0,63; 1,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,16</t>
+          <t>1,15; 2,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,13</t>
+          <t>1,28; 2,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,06</t>
+          <t>1,17; 2,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,55</t>
+          <t>0,8; 1,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,84</t>
+          <t>1,04; 1,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,05</t>
+          <t>1,37; 2,0</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,76</t>
+          <t>1,2; 1,79</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,8; 1,33</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,89</t>
+          <t>1,19; 1,86</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4317; 16161</t>
+          <t>4430; 16839</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4350; 18449</t>
+          <t>4598; 17741</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1801</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2035</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>977; 11894</t>
+          <t>987; 10780</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2976; 14438</t>
+          <t>3286; 15343</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7403; 22336</t>
+          <t>6776; 22175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9865; 27462</t>
+          <t>10255; 26965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1327</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8659; 24963</t>
+          <t>8854; 24788</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1975; 12033</t>
+          <t>1982; 11775</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>872; 7842</t>
+          <t>868; 8674</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10966; 35280</t>
+          <t>11657; 35168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7980; 23286</t>
+          <t>8053; 23294</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5583</t>
+          <t>0; 5586</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2079; 11989</t>
+          <t>2017; 12049</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17325; 35166</t>
+          <t>17770; 35465</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18724; 40591</t>
+          <t>19448; 40758</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2905; 12964</t>
+          <t>2878; 13441</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3987; 15939</t>
+          <t>3997; 16106</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34423; 63999</t>
+          <t>34731; 64959</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>0; 4575</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4927</t>
+          <t>0; 3698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1682</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5031</t>
+          <t>0; 5039</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5025; 18128</t>
+          <t>5125; 19630</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1937</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>315; 5737</t>
+          <t>161; 5813</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5019</t>
+          <t>0; 5754</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5993; 20612</t>
+          <t>6171; 20979</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4028</t>
+          <t>0; 4698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>162; 5817</t>
+          <t>162; 6196</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4754; 18706</t>
+          <t>5421; 21030</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7827; 24921</t>
+          <t>8855; 26198</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>966; 9681</t>
+          <t>974; 9688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1058; 9190</t>
+          <t>1232; 8468</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6458</t>
+          <t>0; 6385</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9933; 24869</t>
+          <t>9255; 25246</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5183; 20030</t>
+          <t>4993; 18006</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>147; 4549</t>
+          <t>161; 4570</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6491; 21027</t>
+          <t>6288; 20680</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21565; 43627</t>
+          <t>21892; 45338</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8088; 23537</t>
+          <t>8254; 23689</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1989; 10732</t>
+          <t>1876; 11101</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4232</t>
+          <t>0; 4641</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1903</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1225</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6020</t>
+          <t>0; 6293</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 813</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4313</t>
+          <t>0; 4251</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7082</t>
+          <t>0; 6880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 1893</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 964</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6096</t>
+          <t>0; 5784</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>990; 9702</t>
+          <t>980; 9989</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6114</t>
+          <t>0; 6156</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2703; 11784</t>
+          <t>2835; 12518</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5901</t>
+          <t>0; 7332</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1713; 12277</t>
+          <t>1043; 11600</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1984; 11068</t>
+          <t>1952; 12139</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3293; 12611</t>
+          <t>3356; 11887</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>955; 9569</t>
+          <t>1024; 9557</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3766; 16425</t>
+          <t>3933; 17124</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3022; 13901</t>
+          <t>3019; 13153</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7872; 20877</t>
+          <t>7758; 20472</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8668; 26090</t>
+          <t>7853; 26075</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2565; 12494</t>
+          <t>2268; 12431</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2995; 16552</t>
+          <t>2898; 16426</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6874; 26951</t>
+          <t>7119; 27600</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10602; 28503</t>
+          <t>10443; 27953</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5921; 19808</t>
+          <t>6186; 19909</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1686; 13155</t>
+          <t>1159; 11106</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5130; 23937</t>
+          <t>4538; 22967</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22075; 45431</t>
+          <t>23073; 46958</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10467; 26508</t>
+          <t>10983; 27625</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6501; 23007</t>
+          <t>6270; 24490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15240; 42518</t>
+          <t>14193; 43213</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6503; 21951</t>
+          <t>6519; 21412</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 7435</t>
+          <t>0; 7145</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>957; 9863</t>
+          <t>1127; 9657</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3371; 19168</t>
+          <t>3518; 20078</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11836; 28638</t>
+          <t>11685; 29328</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2034; 13348</t>
+          <t>2148; 13512</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2290; 13107</t>
+          <t>2176; 13698</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>867; 9243</t>
+          <t>873; 9204</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21903; 45147</t>
+          <t>22211; 45233</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3969; 14949</t>
+          <t>4081; 16348</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4896; 18734</t>
+          <t>5013; 18310</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6799; 24692</t>
+          <t>6864; 22973</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>41158; 71594</t>
+          <t>41915; 72746</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>32497; 59551</t>
+          <t>32323; 60314</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20462; 44332</t>
+          <t>21110; 45565</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38688; 74710</t>
+          <t>39776; 77503</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>42023; 71951</t>
+          <t>43297; 73097</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42517; 72634</t>
+          <t>41378; 72597</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28480; 54585</t>
+          <t>28262; 53496</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>39338; 67432</t>
+          <t>38216; 67394</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>92764; 135990</t>
+          <t>91197; 133070</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82646; 121592</t>
+          <t>82768; 124239</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54591; 89984</t>
+          <t>55294; 91240</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>85001; 134634</t>
+          <t>84783; 132144</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Provincia-trans_dic.xlsx
@@ -722,12 +722,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,71</t>
+          <t>1,7; 5,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,04</t>
+          <t>1,63; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,8</t>
+          <t>0,34; 4,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,33</t>
+          <t>1,04; 4,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,83</t>
+          <t>1,29; 4,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,64</t>
+          <t>1,65; 4,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,03</t>
+          <t>1,61; 4,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,36</t>
+          <t>0,4; 2,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,74</t>
+          <t>0,17; 1,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,8</t>
+          <t>2,45; 6,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,62</t>
+          <t>1,58; 4,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,31</t>
+          <t>0,41; 2,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,89</t>
+          <t>3,25; 6,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,09</t>
+          <t>1,93; 4,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,33</t>
+          <t>0,3; 1,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,58</t>
+          <t>0,44; 1,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,3</t>
+          <t>3,26; 6,0</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,8</t>
+          <t>1,63; 5,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,67</t>
+          <t>0,18; 1,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,17</t>
+          <t>0,92; 3,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,93</t>
+          <t>0,1; 0,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,86</t>
+          <t>1,5; 5,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 7,11</t>
+          <t>2,36; 7,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,63</t>
+          <t>0,26; 2,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,73</t>
+          <t>0,43; 3,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,58</t>
+          <t>2,4; 6,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,67</t>
+          <t>1,28; 4,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,96</t>
+          <t>0,1; 1,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,83</t>
+          <t>0,88; 3,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,03</t>
+          <t>2,85; 5,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,14</t>
+          <t>1,04; 2,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,41</t>
+          <t>0,38; 1,67</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,67</t>
+          <t>0,36; 3,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,66</t>
+          <t>0,97; 4,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,14</t>
+          <t>0,61; 4,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,46</t>
+          <t>0,7; 4,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,62</t>
+          <t>1,27; 4,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,74</t>
+          <t>0,17; 1,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,1</t>
+          <t>0,73; 3,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,46</t>
+          <t>0,55; 2,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,89</t>
+          <t>1,48; 3,75</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,24</t>
+          <t>1,37; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,88</t>
+          <t>0,31; 1,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,55</t>
+          <t>0,47; 2,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,44</t>
+          <t>1,18; 3,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,39</t>
+          <t>1,58; 4,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,88</t>
+          <t>0,76; 2,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,7</t>
+          <t>1,24; 3,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,75</t>
+          <t>1,82; 3,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,05</t>
+          <t>0,82; 2,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,85</t>
+          <t>0,5; 1,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,94</t>
+          <t>1,39; 3,15</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,91</t>
+          <t>0,93; 2,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,25</t>
+          <t>0,12; 1,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,16</t>
+          <t>0,71; 2,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,78</t>
+          <t>1,45; 3,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,66</t>
+          <t>0,26; 1,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,66</t>
+          <t>0,26; 1,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,29</t>
+          <t>0,12; 1,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,99</t>
+          <t>1,48; 2,95</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,03</t>
+          <t>0,25; 0,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,15</t>
+          <t>0,33; 1,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,4</t>
+          <t>0,51; 1,52</t>
         </is>
       </c>
     </row>
@@ -1784,19 +1784,19 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,23</t>
+          <t>1,27; 2,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,77</t>
+          <t>0,94; 1,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,35</t>
+          <t>0,59; 1,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,24</t>
+          <t>1,25; 2,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,17</t>
+          <t>1,26; 2,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,06</t>
+          <t>1,18; 2,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,52</t>
+          <t>0,79; 1,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,84</t>
+          <t>1,2; 2,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,0</t>
+          <t>1,39; 2,05</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,79</t>
+          <t>1,14; 1,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,33</t>
+          <t>0,77; 1,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,86</t>
+          <t>1,32; 1,95</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4430; 16839</t>
+          <t>5023; 17507</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4598; 17741</t>
+          <t>4785; 19875</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>987; 10780</t>
+          <t>968; 12191</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3286; 15343</t>
+          <t>2988; 13932</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6776; 22175</t>
+          <t>7472; 23358</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10255; 26965</t>
+          <t>9582; 27888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47003</t>
+          <t>47955</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8854; 24788</t>
+          <t>7919; 23126</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1982; 11775</t>
+          <t>1992; 12530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>868; 8674</t>
+          <t>871; 9143</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11657; 35168</t>
+          <t>12944; 36224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8053; 23294</t>
+          <t>7956; 22678</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5586</t>
+          <t>0; 5562</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2017; 12049</t>
+          <t>2117; 12993</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17770; 35465</t>
+          <t>17763; 35810</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19448; 40758</t>
+          <t>19227; 41703</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2878; 13441</t>
+          <t>2988; 14122</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3997; 16106</t>
+          <t>4524; 16625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34731; 64959</t>
+          <t>35042; 64537</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>2268</t>
         </is>
       </c>
     </row>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4575</t>
+          <t>0; 4552</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3698</t>
+          <t>0; 4345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5039</t>
+          <t>0; 5700</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5125; 19630</t>
+          <t>5519; 20005</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>161; 5813</t>
+          <t>644; 6444</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5754</t>
+          <t>0; 5498</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6171; 20979</t>
+          <t>6067; 21275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4698</t>
+          <t>0; 4696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>162; 6196</t>
+          <t>646; 6371</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>6900</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5421; 21030</t>
+          <t>5380; 19179</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8855; 26198</t>
+          <t>8707; 25964</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>974; 9688</t>
+          <t>957; 9455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1232; 8468</t>
+          <t>1608; 12402</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6385</t>
+          <t>0; 6421</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9255; 25246</t>
+          <t>9203; 25613</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4993; 18006</t>
+          <t>4952; 18147</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>161; 4570</t>
+          <t>437; 6567</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6288; 20680</t>
+          <t>6389; 23851</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21892; 45338</t>
+          <t>21472; 44775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8254; 23689</t>
+          <t>7863; 22239</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1876; 11101</t>
+          <t>3031; 13232</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>0; 3952</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6293</t>
+          <t>0; 6040</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4251</t>
+          <t>0; 4259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6880</t>
+          <t>0; 6040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>12851</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5784</t>
+          <t>0; 6000</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>980; 9989</t>
+          <t>982; 9754</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6156</t>
+          <t>0; 6541</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2835; 12518</t>
+          <t>2606; 11527</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7332</t>
+          <t>0; 6674</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1043; 11600</t>
+          <t>1713; 12833</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1952; 12139</t>
+          <t>1911; 11017</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3356; 11887</t>
+          <t>3339; 12219</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1024; 9557</t>
+          <t>957; 9268</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3933; 17124</t>
+          <t>4011; 16916</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3019; 13153</t>
+          <t>2965; 13942</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7758; 20472</t>
+          <t>7913; 20011</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>32506</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7853; 26075</t>
+          <t>8422; 25709</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2268; 12431</t>
+          <t>2023; 12282</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2898; 16426</t>
+          <t>3000; 16447</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7119; 27600</t>
+          <t>8464; 27835</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10443; 27953</t>
+          <t>10080; 27453</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6186; 19909</t>
+          <t>5222; 18151</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1159; 11106</t>
+          <t>1166; 11103</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4538; 22967</t>
+          <t>9567; 28274</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23073; 46958</t>
+          <t>22733; 46624</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10983; 27625</t>
+          <t>11090; 28341</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6270; 24490</t>
+          <t>6611; 22096</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14193; 43213</t>
+          <t>20707; 46854</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>15154</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6519; 21412</t>
+          <t>6829; 21511</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 7145</t>
+          <t>0; 7118</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1127; 9657</t>
+          <t>952; 9295</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3518; 20078</t>
+          <t>5690; 21006</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11685; 29328</t>
+          <t>11241; 29148</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2148; 13512</t>
+          <t>2141; 13174</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2176; 13698</t>
+          <t>2129; 13277</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>873; 9204</t>
+          <t>986; 9068</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22211; 45233</t>
+          <t>22361; 44644</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4081; 16348</t>
+          <t>3993; 15634</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5013; 18310</t>
+          <t>5253; 18108</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6864; 22973</t>
+          <t>8254; 24672</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>117633</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>41915; 72746</t>
+          <t>41443; 72470</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>32323; 60314</t>
+          <t>31878; 59707</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21110; 45565</t>
+          <t>19928; 43526</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39776; 77503</t>
+          <t>44235; 80260</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>43297; 73097</t>
+          <t>42484; 72232</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41378; 72597</t>
+          <t>41573; 72617</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28262; 53496</t>
+          <t>27888; 52384</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>38216; 67394</t>
+          <t>44932; 75935</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>91197; 133070</t>
+          <t>92113; 136039</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82768; 124239</t>
+          <t>79250; 120888</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55294; 91240</t>
+          <t>53130; 88717</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>84783; 132144</t>
+          <t>95811; 141205</t>
         </is>
       </c>
     </row>
